--- a/config/auto_configs/2019_Hyundai_Kia_K900(RJ)_G 3.3 T-GDI LAMBDA2.xlsx
+++ b/config/auto_configs/2019_Hyundai_Kia_K900(RJ)_G 3.3 T-GDI LAMBDA2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KMA_0037D</t>
+          <t>KMA_00281</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B135600</t>
+          <t>P040100</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KMA_0037D</t>
+          <t>KMA_00281</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B135700</t>
+          <t>P043E00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KMA_0037D</t>
+          <t>KMA_00281</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B135800</t>
+          <t>P043F00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,17 +586,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KMA_0037D</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B135900</t>
+          <t>P075300</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KMA_0037D</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B149000</t>
+          <t>P075311</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KMA_0037D</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B149300</t>
+          <t>P075312</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,17 +652,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KMA_0037D</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B149400</t>
+          <t>P075313</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -674,17 +674,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C110901</t>
+          <t>P075800</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -696,17 +696,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C123501</t>
+          <t>P075811</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -718,17 +718,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C128302</t>
+          <t>P075812</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -740,17 +740,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C150301</t>
+          <t>P075813</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -762,17 +762,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C152001</t>
+          <t>P076800</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,17 +784,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C152701</t>
+          <t>P076811</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -806,17 +806,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C161308</t>
+          <t>P076812</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -828,17 +828,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C163808</t>
+          <t>P076813</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -850,17 +850,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C164908</t>
+          <t>P077300</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -872,17 +872,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C222808</t>
+          <t>P077311</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -894,17 +894,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ABS/ESC</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KMA_0029C</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C238001</t>
+          <t>P077312</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -916,17 +916,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KMA_0037E</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B135600</t>
+          <t>P077313</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -938,17 +938,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>KMA_0037E</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B135700</t>
+          <t>P160200</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -960,17 +960,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KMA_0037E</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B135800</t>
+          <t>P270900</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -982,17 +982,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KMA_0037E</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B135900</t>
+          <t>P270911</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1004,17 +1004,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KMA_0037E</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B149000</t>
+          <t>P270912</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1026,17 +1026,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KMA_0037E</t>
+          <t>KMA_0029A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B149300</t>
+          <t>P270913</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1048,20 +1048,1428 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>KMA_0029A</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>U000100</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>KMA_0029A</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>U010000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C110901</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C123501</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C128302</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>C150301</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C152001</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>C152701</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>C161308</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>C163808</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>C164908</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C222808</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ABS/ESC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>KMA_0029C</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C238001</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>SRS</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>KMA_0037E</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B135600</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KMA_0037E</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B135700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KMA_0037E</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B135800</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>KMA_0037E</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B135900</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>KMA_0037E</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B149000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>KMA_0037E</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B149300</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>KMA_0037E</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>B149400</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>KMA_0037D</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B135600</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>KMA_0037D</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B135700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>KMA_0037D</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B135800</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>KMA_0037D</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B135900</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>KMA_0037D</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B149000</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>KMA_0037D</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B149300</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>KMA_0037D</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B149400</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>KMA_002AB</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4WD</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>KMA_0029D</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>KMA_001CE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AAF</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KMA_00336</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AFLS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KMA_002A3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AHLS</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KMA_002A4</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KMA_00215</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>APSM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KMA_002AF</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KMA_002B3</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KMA_002A8</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BCW</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>KMA_002A1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CCP</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>KMA_002A9</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KMA_0024B</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DDM</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>KMA_001C6</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EASM</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KMA_002B1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ECS</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>KMA_0029F</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EDSM</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>KMA_002B0</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>KMA_0029E</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KMA_002A6</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FCA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KMA_0029B</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KMA_002AE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KMA_00290</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>IBU-SKU</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KMA_00291</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>KMA_00294</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MFC</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KMA_002A2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MFS</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>KMA_001A6</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KMA_002B2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>KMA_00180</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PSB</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>KMA_002A7</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>KMA_002AD</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PTM</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>KMA_001A8</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>RRC</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>KMA_002AA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>KMA_001FF</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>RWPC</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KMA_002AC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SCM</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>KMA_0023C</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SVMS</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>KMA_002A0</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SWRC</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>KMA_00206</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>KMA_001C2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>00</t>
         </is>
